--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_27_8.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_27_8.xlsx
@@ -517,52 +517,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9939919440978767</v>
+        <v>0.9996525246040266</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6997821869252651</v>
+        <v>0.6196235528296539</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9971772158163131</v>
+        <v>0.9993829078684286</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9003011145378196</v>
+        <v>0.9984640832560144</v>
       </c>
       <c r="F2" t="n">
-        <v>0.962955245088891</v>
+        <v>0.9990819237239658</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04017589748205209</v>
+        <v>0.00020627640520529</v>
       </c>
       <c r="H2" t="n">
-        <v>2.007557898406672</v>
+        <v>0.2258078904472654</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01224644847294668</v>
+        <v>0.0005731548747778581</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2380151034877102</v>
+        <v>0.0007098546522777664</v>
       </c>
       <c r="K2" t="n">
-        <v>0.125130594195225</v>
+        <v>0.0006415047635278123</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1311509751868877</v>
+        <v>0.008078073353461619</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2004392613288427</v>
+        <v>0.01436232589817158</v>
       </c>
       <c r="N2" t="n">
-        <v>1.002059904880728</v>
+        <v>1.000245276750099</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2089723756500826</v>
+        <v>0.01497375984576998</v>
       </c>
       <c r="P2" t="n">
-        <v>194.4289760565826</v>
+        <v>132.9725870314125</v>
       </c>
       <c r="Q2" t="n">
-        <v>309.0033035941934</v>
+        <v>203.6673848737681</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +572,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9940504935379464</v>
+        <v>0.9996547924715897</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6997515351341272</v>
+        <v>0.6195984529875802</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9971255967680848</v>
+        <v>0.9993842386585904</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9015024292983188</v>
+        <v>0.9984827714571333</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9633465669465715</v>
+        <v>0.9990889866739766</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03978437710671056</v>
+        <v>0.000204930101053129</v>
       </c>
       <c r="H3" t="n">
-        <v>2.007762867075149</v>
+        <v>0.2258227907977771</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01247039404342453</v>
+        <v>0.0005719188375161997</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2351471571138262</v>
+        <v>0.0007012175262363321</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1238087785511308</v>
+        <v>0.0006365695351652278</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1308748646752207</v>
+        <v>0.008101958681040472</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1994602143453941</v>
+        <v>0.01431537987805874</v>
       </c>
       <c r="N3" t="n">
-        <v>1.00203983078699</v>
+        <v>1.000243675902407</v>
       </c>
       <c r="O3" t="n">
-        <v>0.207951648609642</v>
+        <v>0.01492481523638928</v>
       </c>
       <c r="P3" t="n">
-        <v>194.4485619575221</v>
+        <v>132.9856832148841</v>
       </c>
       <c r="Q3" t="n">
-        <v>309.0228894951329</v>
+        <v>203.6804810572397</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +627,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9941145330385455</v>
+        <v>0.99965723852133</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6997163423506176</v>
+        <v>0.6195707639359538</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9970659246126977</v>
+        <v>0.9993856630994272</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9028338498568701</v>
+        <v>0.9985034378220926</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9637786870507883</v>
+        <v>0.9990967691110065</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03935614467132988</v>
+        <v>0.0002034780202634349</v>
       </c>
       <c r="H4" t="n">
-        <v>2.007998201380525</v>
+        <v>0.2258392282149273</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01272927744671137</v>
+        <v>0.0005705958175525863</v>
       </c>
       <c r="J4" t="n">
-        <v>0.23196860400804</v>
+        <v>0.0006916661521989765</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1223491536856375</v>
+        <v>0.0006311315660586644</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1305605688520416</v>
+        <v>0.008128415229060503</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1983838316782138</v>
+        <v>0.01426457220751589</v>
       </c>
       <c r="N4" t="n">
-        <v>1.002017874386784</v>
+        <v>1.000241949279061</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2068294421039005</v>
+        <v>0.01487184457812505</v>
       </c>
       <c r="P4" t="n">
-        <v>194.4702063240381</v>
+        <v>132.9999051348969</v>
       </c>
       <c r="Q4" t="n">
-        <v>309.044533861649</v>
+        <v>203.6947029772525</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +682,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9941844285979342</v>
+        <v>0.9996598521809764</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6996759205527925</v>
+        <v>0.6195399647804692</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9969967044587642</v>
+        <v>0.9993871771193007</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9043085417185791</v>
+        <v>0.9985261878938784</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9642554606854827</v>
+        <v>0.9991053063613438</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03888875274385776</v>
+        <v>0.0002019264389931247</v>
       </c>
       <c r="H5" t="n">
-        <v>2.008268502128708</v>
+        <v>0.2258575119240772</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01302958416280207</v>
+        <v>0.0005691895966228589</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2284480136378467</v>
+        <v>0.000681151751363135</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1207386971352006</v>
+        <v>0.0006251661720039627</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1302046145578716</v>
+        <v>0.008157899387322176</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1972023142456948</v>
+        <v>0.01421008230071609</v>
       </c>
       <c r="N5" t="n">
-        <v>1.001993910194994</v>
+        <v>1.00024010434284</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2055976250282009</v>
+        <v>0.01481503492318312</v>
       </c>
       <c r="P5" t="n">
-        <v>194.4941004054265</v>
+        <v>133.0152141805741</v>
       </c>
       <c r="Q5" t="n">
-        <v>309.0684279430374</v>
+        <v>203.7100120229297</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +737,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9942604680011708</v>
+        <v>0.9996626476924613</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6996293098433884</v>
+        <v>0.6195058274092411</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9969161467419646</v>
+        <v>0.9993887907474928</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9059413322177094</v>
+        <v>0.9985513265590346</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9647806584413349</v>
+        <v>0.9991146890114398</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03838027690428567</v>
+        <v>0.0002002669026158527</v>
       </c>
       <c r="H6" t="n">
-        <v>2.008580188157115</v>
+        <v>0.2258777773422959</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01337907808925442</v>
+        <v>0.0005676908595347235</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2245499881200822</v>
+        <v>0.0006695334143126081</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1189646725150491</v>
+        <v>0.0006186100558203064</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1298044455161438</v>
+        <v>0.008190490360948616</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1959088484583728</v>
+        <v>0.01415156891004855</v>
       </c>
       <c r="N6" t="n">
-        <v>1.001967839542456</v>
+        <v>1.000238131040616</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2042490937244693</v>
+        <v>0.01475403049633545</v>
       </c>
       <c r="P6" t="n">
-        <v>194.5204231472436</v>
+        <v>133.0317191360162</v>
       </c>
       <c r="Q6" t="n">
-        <v>309.0947506848544</v>
+        <v>203.7265169783719</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +792,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.994343028744702</v>
+        <v>0.9996656049583349</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6995754031251659</v>
+        <v>0.6194680245092782</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9968221115693422</v>
+        <v>0.999390486509652</v>
       </c>
       <c r="E7" t="n">
-        <v>0.907748832216978</v>
+        <v>0.9985789861982017</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9653590758228183</v>
+        <v>0.9991249604530441</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03782819283213461</v>
+        <v>0.0001985113418460435</v>
       </c>
       <c r="H7" t="n">
-        <v>2.008940662630087</v>
+        <v>0.2259002187767141</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01378704299950894</v>
+        <v>0.0005661158364574686</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2202348716833681</v>
+        <v>0.0006567499586858222</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1170108814638859</v>
+        <v>0.0006114328975716455</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1293537148596335</v>
+        <v>0.008226645277785338</v>
       </c>
       <c r="M7" t="n">
-        <v>0.194494711578836</v>
+        <v>0.01408940530491062</v>
       </c>
       <c r="N7" t="n">
-        <v>1.001939533001816</v>
+        <v>1.000236043558822</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2027747541103037</v>
+        <v>0.01468922045783039</v>
       </c>
       <c r="P7" t="n">
-        <v>194.5494012244773</v>
+        <v>133.0493286434118</v>
       </c>
       <c r="Q7" t="n">
-        <v>309.1237287620881</v>
+        <v>203.7441264857674</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +847,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9944322782577323</v>
+        <v>0.9996687110932942</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6995128569227107</v>
+        <v>0.619426029531724</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9967118358839608</v>
+        <v>0.9993922477982992</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9097480104393536</v>
+        <v>0.9986094289690005</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9659947425948612</v>
+        <v>0.9991361988394224</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03723138092754544</v>
+        <v>0.0001966674059561574</v>
       </c>
       <c r="H8" t="n">
-        <v>2.009358909373904</v>
+        <v>0.2259251488094788</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01426546621962091</v>
+        <v>0.0005644799524097044</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2154621542223527</v>
+        <v>0.000642680223093483</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1148637121524205</v>
+        <v>0.0006035800877515937</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1288427839858838</v>
+        <v>0.008266816553261882</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1929543493356536</v>
+        <v>0.01402381567035725</v>
       </c>
       <c r="N8" t="n">
-        <v>1.001908933168778</v>
+        <v>1.000233850992969</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2011688154574396</v>
+        <v>0.01462083853674482</v>
       </c>
       <c r="P8" t="n">
-        <v>194.5812065999799</v>
+        <v>133.0679931012812</v>
       </c>
       <c r="Q8" t="n">
-        <v>309.1555341375907</v>
+        <v>203.7627909436368</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +902,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9945283554653643</v>
+        <v>0.999671940048835</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6994401109770303</v>
+        <v>0.6193796579795621</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9965819832219223</v>
+        <v>0.9993940617112481</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9119578938487697</v>
+        <v>0.9986428738949769</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9666922559795289</v>
+        <v>0.999148468874991</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03658891219771479</v>
+        <v>0.0001947505584635541</v>
       </c>
       <c r="H9" t="n">
-        <v>2.009845361847633</v>
+        <v>0.2259526769659889</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01482882276098204</v>
+        <v>0.0005627951909358248</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2101864119113971</v>
+        <v>0.0006272229814217622</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1125076359820686</v>
+        <v>0.0005950064142220643</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1282639185933207</v>
+        <v>0.008311270312408484</v>
       </c>
       <c r="M9" t="n">
-        <v>0.191282284066546</v>
+        <v>0.01395530574597182</v>
       </c>
       <c r="N9" t="n">
-        <v>1.001875992411875</v>
+        <v>1.000231571730234</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1994255669081738</v>
+        <v>0.01454941200304321</v>
       </c>
       <c r="P9" t="n">
-        <v>194.6160200597793</v>
+        <v>133.0875820112509</v>
       </c>
       <c r="Q9" t="n">
-        <v>309.1903475973902</v>
+        <v>203.7823798536066</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +957,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9946312682272785</v>
+        <v>0.9996752566459216</v>
       </c>
       <c r="C10" t="n">
-        <v>0.69935521472712</v>
+        <v>0.619328294695726</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9964285151778685</v>
+        <v>0.9993959077740906</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9143987171584567</v>
+        <v>0.9986795806179176</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9674562543693981</v>
+        <v>0.9991618313471722</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03590073408492502</v>
+        <v>0.000192781683163412</v>
       </c>
       <c r="H10" t="n">
-        <v>2.010413063461694</v>
+        <v>0.2259831684300523</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01549463295809514</v>
+        <v>0.0005610805686563456</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2043593376170638</v>
+        <v>0.0006102582350242733</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1099269852875795</v>
+        <v>0.0005856694018403094</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1276029763836417</v>
+        <v>0.008360582159162031</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1894748903810872</v>
+        <v>0.01388458437128789</v>
       </c>
       <c r="N10" t="n">
-        <v>1.001840708036362</v>
+        <v>1.000229230602879</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1975412287317043</v>
+        <v>0.01447567987302556</v>
       </c>
       <c r="P10" t="n">
-        <v>194.6539950712978</v>
+        <v>133.1079043692804</v>
       </c>
       <c r="Q10" t="n">
-        <v>309.2283226089086</v>
+        <v>203.802702211636</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1012,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9947407623652339</v>
+        <v>0.9996785952148655</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6992557782893085</v>
+        <v>0.6192714176533343</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9962462379584414</v>
+        <v>0.999397717799674</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9170917715792571</v>
+        <v>0.9987197678195708</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9682908665494226</v>
+        <v>0.9991763247302254</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03516854628024342</v>
+        <v>0.0001907997644196739</v>
       </c>
       <c r="H11" t="n">
-        <v>2.011077995379202</v>
+        <v>0.2260169330993764</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01628542971415134</v>
+        <v>0.0005593994177656133</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1979301019872632</v>
+        <v>0.0005916849157559835</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1071078137676265</v>
+        <v>0.0005755421667607984</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1268538721191665</v>
+        <v>0.00841532106893704</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1875327872139787</v>
+        <v>0.01381302879240009</v>
       </c>
       <c r="N11" t="n">
-        <v>1.001803167189063</v>
+        <v>1.000226873965977</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1955164462120643</v>
+        <v>0.01440107802500404</v>
       </c>
       <c r="P11" t="n">
-        <v>194.6952063348703</v>
+        <v>133.1285720672971</v>
       </c>
       <c r="Q11" t="n">
-        <v>309.2695338724811</v>
+        <v>203.8233699096528</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1067,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.994856303536546</v>
+        <v>0.999681890456331</v>
       </c>
       <c r="C12" t="n">
-        <v>0.69913886994233</v>
+        <v>0.6192084915912406</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9960286826138195</v>
+        <v>0.9993994574225031</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9200593131336021</v>
+        <v>0.9987637442455649</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9691998660265239</v>
+        <v>0.9991920206828229</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03439592193566147</v>
+        <v>0.0001888435667386844</v>
       </c>
       <c r="H12" t="n">
-        <v>2.011859762033762</v>
+        <v>0.2260542887280995</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01722927810799013</v>
+        <v>0.0005577836569192491</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1908455723369347</v>
+        <v>0.0005713603306476724</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1040373751868944</v>
+        <v>0.0005645746375671704</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1259976213338014</v>
+        <v>0.008475907125305387</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1854613758593996</v>
+        <v>0.01374203648440377</v>
       </c>
       <c r="N12" t="n">
-        <v>1.001763553073184</v>
+        <v>1.000224547913178</v>
       </c>
       <c r="O12" t="n">
-        <v>0.193356850587708</v>
+        <v>0.01432706342748198</v>
       </c>
       <c r="P12" t="n">
-        <v>194.7396345400243</v>
+        <v>133.1491831496836</v>
       </c>
       <c r="Q12" t="n">
-        <v>309.3139620776351</v>
+        <v>203.8439809920392</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1122,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9949770420157561</v>
+        <v>0.9996850340149328</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6990009387391438</v>
+        <v>0.6191389764110653</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9957679101416198</v>
+        <v>0.9994010345310025</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9233253986767178</v>
+        <v>0.9988117534823089</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9701865962519368</v>
+        <v>0.9992089498939928</v>
       </c>
       <c r="G13" t="n">
-        <v>0.03358854316923372</v>
+        <v>0.0001869774145580048</v>
       </c>
       <c r="H13" t="n">
-        <v>2.012782108624582</v>
+        <v>0.226095555941951</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01836062093696455</v>
+        <v>0.0005563188393041603</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1830483167814625</v>
+        <v>0.0005491719013669126</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1007043759616985</v>
+        <v>0.0005527453703355364</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1250183623148396</v>
+        <v>0.008542979118036798</v>
       </c>
       <c r="M13" t="n">
-        <v>0.183271774065822</v>
+        <v>0.01367396850069521</v>
       </c>
       <c r="N13" t="n">
-        <v>1.001722157023169</v>
+        <v>1.000222328930636</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1910740329126774</v>
+        <v>0.0142560976487868</v>
       </c>
       <c r="P13" t="n">
-        <v>194.7871404945301</v>
+        <v>133.1690454523372</v>
       </c>
       <c r="Q13" t="n">
-        <v>309.3614680321409</v>
+        <v>203.8638432946928</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1177,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9951014862249471</v>
+        <v>0.9996878813068695</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6988375452124265</v>
+        <v>0.6190620386544441</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9954537219858731</v>
+        <v>0.9994023499934314</v>
       </c>
       <c r="E14" t="n">
-        <v>0.926913144052726</v>
+        <v>0.998863997427704</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9712526350966899</v>
+        <v>0.9992271018985582</v>
       </c>
       <c r="G14" t="n">
-        <v>0.03275638416936105</v>
+        <v>0.0001852871390678103</v>
       </c>
       <c r="H14" t="n">
-        <v>2.013874721890099</v>
+        <v>0.2261412295178193</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01972370391100057</v>
+        <v>0.0005550970384334145</v>
       </c>
       <c r="J14" t="n">
-        <v>0.174483149949361</v>
+        <v>0.0005250263167593566</v>
       </c>
       <c r="K14" t="n">
-        <v>0.09710348632430629</v>
+        <v>0.0005400616775963856</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1238952565272366</v>
+        <v>0.00861727572113332</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1809872486374691</v>
+        <v>0.01361202185818882</v>
       </c>
       <c r="N14" t="n">
-        <v>1.001679490437161</v>
+        <v>1.000220319077504</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1886922505072198</v>
+        <v>0.01419151380946168</v>
       </c>
       <c r="P14" t="n">
-        <v>194.837314798859</v>
+        <v>133.1872076661676</v>
       </c>
       <c r="Q14" t="n">
-        <v>309.4116423364698</v>
+        <v>203.8820055085232</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1232,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9952274768734545</v>
+        <v>0.9996902554031447</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6986432696394802</v>
+        <v>0.6189772802526564</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9950731320183144</v>
+        <v>0.9994032784518498</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9308454528837777</v>
+        <v>0.9989207220953997</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9723978602677179</v>
+        <v>0.9992464822519298</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03191388412265862</v>
+        <v>0.0001838777729632114</v>
       </c>
       <c r="H15" t="n">
-        <v>2.015173843540948</v>
+        <v>0.2261915457664928</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02137486642422566</v>
+        <v>0.0005542346867012221</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1650953931150736</v>
+        <v>0.000498809876694902</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09323511935894443</v>
+        <v>0.000526519677512899</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1226054529072107</v>
+        <v>0.008699481009823949</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1786445748481006</v>
+        <v>0.0135601538694519</v>
       </c>
       <c r="N15" t="n">
-        <v>1.001636293643387</v>
+        <v>1.000218643244839</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1862498442446346</v>
+        <v>0.01413743769306269</v>
       </c>
       <c r="P15" t="n">
-        <v>194.8894282498511</v>
+        <v>133.2024785969182</v>
       </c>
       <c r="Q15" t="n">
-        <v>309.4637557874619</v>
+        <v>203.8972764392738</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1287,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9953518451821747</v>
+        <v>0.9996919124575367</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6984112718058988</v>
+        <v>0.6188837514961414</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9946097443949126</v>
+        <v>0.9994036492031521</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9351431427461886</v>
+        <v>0.9989820988087431</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9736190107086076</v>
+        <v>0.9992670192769109</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03108223266958259</v>
+        <v>0.0001828940738950633</v>
       </c>
       <c r="H16" t="n">
-        <v>2.016725214122358</v>
+        <v>0.226247068476592</v>
       </c>
       <c r="I16" t="n">
-        <v>0.02338524068017737</v>
+        <v>0.0005538903330702257</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1548353476530024</v>
+        <v>0.000470443400661018</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0891102903342432</v>
+        <v>0.0005121694544454011</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1211177252864454</v>
+        <v>0.008790383176266096</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1763015390448495</v>
+        <v>0.01352383355025724</v>
       </c>
       <c r="N16" t="n">
-        <v>1.001593653080397</v>
+        <v>1.000217473559386</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1838070605564864</v>
+        <v>0.01409957114268649</v>
       </c>
       <c r="P16" t="n">
-        <v>194.9422378396943</v>
+        <v>133.2132068077696</v>
       </c>
       <c r="Q16" t="n">
-        <v>309.5165653773051</v>
+        <v>203.9080046501252</v>
       </c>
     </row>
     <row r="17">
@@ -1342,52 +1342,52 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9954701253984096</v>
+        <v>0.9996925330455952</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6981330920591997</v>
+        <v>0.6187806481852228</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9940423075772002</v>
+        <v>0.9994032106530061</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9398245189306437</v>
+        <v>0.999048210648724</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9749089407743906</v>
+        <v>0.9992885992025183</v>
       </c>
       <c r="G17" t="n">
-        <v>0.03029129231898936</v>
+        <v>0.000182525666015494</v>
       </c>
       <c r="H17" t="n">
-        <v>2.018585403369435</v>
+        <v>0.2263082750557844</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02584702496745167</v>
+        <v>0.0005542976582347569</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1436593126166764</v>
+        <v>0.0004398884911160436</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08475313596815204</v>
+        <v>0.0004970905057402623</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1193934632536093</v>
+        <v>0.008890950776811851</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1740439378978463</v>
+        <v>0.01351020599456181</v>
       </c>
       <c r="N17" t="n">
-        <v>1.001553099863402</v>
+        <v>1.000217035497227</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1814533486547766</v>
+        <v>0.01408536343373218</v>
       </c>
       <c r="P17" t="n">
-        <v>194.9937899799611</v>
+        <v>133.2172395182573</v>
       </c>
       <c r="Q17" t="n">
-        <v>309.568117517572</v>
+        <v>203.9120373606129</v>
       </c>
     </row>
     <row r="18">
@@ -1397,52 +1397,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9955760527102757</v>
+        <v>0.9996917130562939</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6977981298794629</v>
+        <v>0.6186668389977041</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9933436701123158</v>
+        <v>0.9994016610608389</v>
       </c>
       <c r="E18" t="n">
-        <v>0.944899958216515</v>
+        <v>0.9991191386077561</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9762538787102424</v>
+        <v>0.9993110224064664</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02958295589679028</v>
+        <v>0.0001830124470864611</v>
       </c>
       <c r="H18" t="n">
-        <v>2.020825297007693</v>
+        <v>0.2263758371057965</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02887801393374299</v>
+        <v>0.0005557369186936657</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1315425151091406</v>
+        <v>0.0004071077157955681</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0802101747993532</v>
+        <v>0.0004814223172446169</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1173962354560542</v>
+        <v>0.00900216321610584</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1719969647894703</v>
+        <v>0.0135282093081997</v>
       </c>
       <c r="N18" t="n">
-        <v>1.001516781927905</v>
+        <v>1.000217614313204</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1793192316633586</v>
+        <v>0.01410413318570363</v>
       </c>
       <c r="P18" t="n">
-        <v>195.0411137955889</v>
+        <v>133.21191278114</v>
       </c>
       <c r="Q18" t="n">
-        <v>309.6154413331998</v>
+        <v>203.9067106234956</v>
       </c>
     </row>
     <row r="19">
@@ -1452,52 +1452,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9956609637629095</v>
+        <v>0.9996889322569843</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6973929938295492</v>
+        <v>0.6185416307174871</v>
       </c>
       <c r="D19" t="n">
-        <v>0.992478560598848</v>
+        <v>0.9993986365098383</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9503702283599207</v>
+        <v>0.9991947145967442</v>
       </c>
       <c r="F19" t="n">
-        <v>0.977631358490994</v>
+        <v>0.9993340061672059</v>
       </c>
       <c r="G19" t="n">
-        <v>0.02901515529684882</v>
+        <v>0.0001846632496809353</v>
       </c>
       <c r="H19" t="n">
-        <v>2.023534443638947</v>
+        <v>0.2264501661496493</v>
       </c>
       <c r="I19" t="n">
-        <v>0.03263123004617797</v>
+        <v>0.000558546120207247</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1184831222357635</v>
+        <v>0.0003721787604379538</v>
       </c>
       <c r="K19" t="n">
-        <v>0.07555729306559744</v>
+        <v>0.0004653624403226004</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1150723509159529</v>
+        <v>0.00912490619547783</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1703383553309378</v>
+        <v>0.01358908568230164</v>
       </c>
       <c r="N19" t="n">
-        <v>1.001487669567003</v>
+        <v>1.000219577230364</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1775900117663815</v>
+        <v>0.01416760119308255</v>
       </c>
       <c r="P19" t="n">
-        <v>195.0798739781171</v>
+        <v>133.1939533271783</v>
       </c>
       <c r="Q19" t="n">
-        <v>309.6542015157279</v>
+        <v>203.8887511695339</v>
       </c>
     </row>
     <row r="20">
@@ -1507,52 +1507,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9957129854172557</v>
+        <v>0.9996835233924448</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6969007074901324</v>
+        <v>0.6184038777048136</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9914009586963182</v>
+        <v>0.9993935931621604</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9562197769064849</v>
+        <v>0.9992747748623404</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9790065150223073</v>
+        <v>0.9993571312095821</v>
       </c>
       <c r="G20" t="n">
-        <v>0.02866728625469779</v>
+        <v>0.0001878741853223558</v>
       </c>
       <c r="H20" t="n">
-        <v>2.026826364657397</v>
+        <v>0.2265319422885926</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03730632927974538</v>
+        <v>0.0005632303791029753</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1045182629877131</v>
+        <v>0.0003351773069291355</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0709122588552866</v>
+        <v>0.0004492038430160554</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1123615666622051</v>
+        <v>0.009260526230111</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1693141643652349</v>
+        <v>0.01370672044372233</v>
       </c>
       <c r="N20" t="n">
-        <v>1.001469833571227</v>
+        <v>1.000223395252392</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1765222188709011</v>
+        <v>0.01429024390983445</v>
       </c>
       <c r="P20" t="n">
-        <v>195.1039973161887</v>
+        <v>133.1594760923508</v>
       </c>
       <c r="Q20" t="n">
-        <v>309.6783248537995</v>
+        <v>203.8542739347065</v>
       </c>
     </row>
     <row r="21">
@@ -1562,52 +1562,52 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9957157958054126</v>
+        <v>0.9996746316993299</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6962997253752337</v>
+        <v>0.6182522443108385</v>
       </c>
       <c r="D21" t="n">
-        <v>0.990051025881737</v>
+        <v>0.9993859495626848</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9624076667737123</v>
+        <v>0.9993586889080358</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9803263237097145</v>
+        <v>0.9993798025760621</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02864849317615275</v>
+        <v>0.0001931526784565467</v>
       </c>
       <c r="H21" t="n">
-        <v>2.030845134826993</v>
+        <v>0.2266219584214779</v>
       </c>
       <c r="I21" t="n">
-        <v>0.04316291681174571</v>
+        <v>0.0005703297506167793</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0897456680856628</v>
+        <v>0.0002963947518449449</v>
       </c>
       <c r="K21" t="n">
-        <v>0.06645417981884656</v>
+        <v>0.0004333622512308621</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1091864689602755</v>
+        <v>0.009410172643220164</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1692586576106308</v>
+        <v>0.01389793792102075</v>
       </c>
       <c r="N21" t="n">
-        <v>1.001468870009573</v>
+        <v>1.000229671741649</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1764643490788386</v>
+        <v>0.01448960191101621</v>
       </c>
       <c r="P21" t="n">
-        <v>195.1053088628102</v>
+        <v>133.1040592034252</v>
       </c>
       <c r="Q21" t="n">
-        <v>309.679636400421</v>
+        <v>203.7988570457808</v>
       </c>
     </row>
     <row r="22">
@@ -1617,52 +1617,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9956470914740125</v>
+        <v>0.9996611764553484</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6955627190413785</v>
+        <v>0.6180858470395862</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9883497931308866</v>
+        <v>0.9993748353024681</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9688557458429216</v>
+        <v>0.999445749861587</v>
       </c>
       <c r="F22" t="n">
-        <v>0.981512396459534</v>
+        <v>0.999401206399718</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02910791935657892</v>
+        <v>0.0002011402925202427</v>
       </c>
       <c r="H22" t="n">
-        <v>2.035773499575085</v>
+        <v>0.226720739029681</v>
       </c>
       <c r="I22" t="n">
-        <v>0.05054359413882602</v>
+        <v>0.0005806526701564314</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0743519131821842</v>
+        <v>0.0002561577903351231</v>
       </c>
       <c r="K22" t="n">
-        <v>0.06244783699650049</v>
+        <v>0.0004184063535659507</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1054624744198378</v>
+        <v>0.009575195108263837</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1706104315585038</v>
+        <v>0.01418239375141738</v>
       </c>
       <c r="N22" t="n">
-        <v>1.001492425780339</v>
+        <v>1.000239169560931</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1778736708422304</v>
+        <v>0.01478616761501756</v>
       </c>
       <c r="P22" t="n">
-        <v>195.0734899979821</v>
+        <v>133.0230158412747</v>
       </c>
       <c r="Q22" t="n">
-        <v>309.647817535593</v>
+        <v>203.7178136836303</v>
       </c>
     </row>
     <row r="23">
@@ -1672,52 +1672,52 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9954764415906568</v>
+        <v>0.999641780908291</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6946544721243385</v>
+        <v>0.617902865384834</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9861934091401081</v>
+        <v>0.9993592063497465</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9754295834664193</v>
+        <v>0.9995346942754797</v>
       </c>
       <c r="F23" t="n">
-        <v>0.982450697979473</v>
+        <v>0.9994202350781576</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03024905591234921</v>
+        <v>0.0002126543270974518</v>
       </c>
       <c r="H23" t="n">
-        <v>2.041846950891423</v>
+        <v>0.2268293648443379</v>
       </c>
       <c r="I23" t="n">
-        <v>0.05989891275778764</v>
+        <v>0.0005951688339215997</v>
       </c>
       <c r="J23" t="n">
-        <v>0.05865792989425925</v>
+        <v>0.0002150503499461436</v>
       </c>
       <c r="K23" t="n">
-        <v>0.05927842132602344</v>
+        <v>0.0004051100859449609</v>
       </c>
       <c r="L23" t="n">
-        <v>0.101081359166791</v>
+        <v>0.009757198669428006</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1739225572269141</v>
+        <v>0.01458267215216237</v>
       </c>
       <c r="N23" t="n">
-        <v>1.001550934311775</v>
+        <v>1.000252860535324</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1813268005573902</v>
+        <v>0.01520348669597279</v>
       </c>
       <c r="P23" t="n">
-        <v>194.9965806090028</v>
+        <v>132.9116851760475</v>
       </c>
       <c r="Q23" t="n">
-        <v>309.5709081466137</v>
+        <v>203.6064830184031</v>
       </c>
     </row>
     <row r="24">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9951620759524723</v>
+        <v>0.9996147118784321</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6935297646444433</v>
+        <v>0.6177017450593756</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9834440614992811</v>
+        <v>0.9993377393944971</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9819112917746781</v>
+        <v>0.9996237558461978</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9829756209187578</v>
+        <v>0.9994354228762006</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03235122038240933</v>
+        <v>0.0002287236725429234</v>
       </c>
       <c r="H24" t="n">
-        <v>2.049367874988285</v>
+        <v>0.2269487585574757</v>
       </c>
       <c r="I24" t="n">
-        <v>0.07182676201108371</v>
+        <v>0.000615107331624545</v>
       </c>
       <c r="J24" t="n">
-        <v>0.04318389057460618</v>
+        <v>0.000173888763186305</v>
       </c>
       <c r="K24" t="n">
-        <v>0.05750532498736468</v>
+        <v>0.0003944976291737186</v>
       </c>
       <c r="L24" t="n">
-        <v>0.09591641429927683</v>
+        <v>0.009957628383230908</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1798644500239259</v>
+        <v>0.01512361307832633</v>
       </c>
       <c r="N24" t="n">
-        <v>1.001658716816295</v>
+        <v>1.000271968085813</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1875216520321845</v>
+        <v>0.01576745659726564</v>
       </c>
       <c r="P24" t="n">
-        <v>194.8622070688129</v>
+        <v>132.7659919062817</v>
       </c>
       <c r="Q24" t="n">
-        <v>309.4365346064237</v>
+        <v>203.4607897486373</v>
       </c>
     </row>
     <row r="25">
@@ -1782,52 +1782,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9946463844513803</v>
+        <v>0.9995777590892847</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6921298222069583</v>
+        <v>0.6174810107854549</v>
       </c>
       <c r="D25" t="n">
-        <v>0.979917268446346</v>
+        <v>0.9993086682038698</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9879587091034273</v>
+        <v>0.9997104729527009</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9828478288552203</v>
+        <v>0.9994447800061004</v>
       </c>
       <c r="G25" t="n">
-        <v>0.03579965182475255</v>
+        <v>0.0002506604444582189</v>
       </c>
       <c r="H25" t="n">
-        <v>2.058729296513889</v>
+        <v>0.2270797959576991</v>
       </c>
       <c r="I25" t="n">
-        <v>0.08712750290623199</v>
+        <v>0.0006421086394862905</v>
       </c>
       <c r="J25" t="n">
-        <v>0.02874665133503982</v>
+        <v>0.0001338107174690991</v>
       </c>
       <c r="K25" t="n">
-        <v>0.05793698385195298</v>
+        <v>0.0003879593451984779</v>
       </c>
       <c r="L25" t="n">
-        <v>0.08982486744000141</v>
+        <v>0.01017826790626416</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1892079592003268</v>
+        <v>0.01583225961315121</v>
       </c>
       <c r="N25" t="n">
-        <v>1.001835525330955</v>
+        <v>1.000298052407564</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1972629337379553</v>
+        <v>0.01650627168217857</v>
       </c>
       <c r="P25" t="n">
-        <v>194.6596342223767</v>
+        <v>132.5828226912614</v>
       </c>
       <c r="Q25" t="n">
-        <v>309.2339617599875</v>
+        <v>203.2776205336171</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9938492417759843</v>
+        <v>0.9995281397866254</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6903774088792278</v>
+        <v>0.617238345815414</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9753633276616596</v>
+        <v>0.9992697967101576</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9930409741652156</v>
+        <v>0.9997914171999154</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9817192792867664</v>
+        <v>0.9994457141844161</v>
       </c>
       <c r="G26" t="n">
-        <v>0.04113014856563007</v>
+        <v>0.0002801166059590391</v>
       </c>
       <c r="H26" t="n">
-        <v>2.070447692505544</v>
+        <v>0.2272238523664963</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1068844512024603</v>
+        <v>0.0006782124641361258</v>
       </c>
       <c r="J26" t="n">
-        <v>0.01661355838193555</v>
+        <v>9.640071416955372e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.06174902359734359</v>
+        <v>0.0003873065891528397</v>
       </c>
       <c r="L26" t="n">
-        <v>0.08263506089696644</v>
+        <v>0.01042101414424693</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2028056916499881</v>
+        <v>0.01673668443745771</v>
       </c>
       <c r="N26" t="n">
-        <v>1.002108831391091</v>
+        <v>1.000333077797676</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2114395498091853</v>
+        <v>0.01744919974367328</v>
       </c>
       <c r="P26" t="n">
-        <v>194.3820277692948</v>
+        <v>132.360609183265</v>
       </c>
       <c r="Q26" t="n">
-        <v>308.9563553069056</v>
+        <v>203.0554070256206</v>
       </c>
     </row>
   </sheetData>
